--- a/templates/課題シート.xlsx
+++ b/templates/課題シート.xlsx
@@ -10,9 +10,10 @@
     <sheet name="使い方" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="登録" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="更新" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="記入例（登録）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="記入例（更新）" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="_マスタ" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="プロジェクト" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="記入例（登録）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="記入例（更新）" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="_マスタ" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -532,47 +533,71 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>■ 共通</t>
+          <t>■ 「プロジェクト」シート：どのプロジェクト向けのブックか</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・列は見出しの名前で読みます。要らない列は消して構いません。</t>
+          <t xml:space="preserve">  ・プロジェクトキーを書きます。取り込むとき、設定ファイルの project_key と違えば何も送りません。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・見出しが # で始まる列は読み飛ばします（メモ用）。</t>
+          <t xml:space="preserve">  ・backlog-issue-sheet template で作ったひな形と、書き出したファイルには、はじめから入っています。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ・カテゴリーなど複数の値は、改行（Alt+Enter）か「,」で区切ります。</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・カスタム属性は、その名前を見出しにした列を足すと使えます。</t>
+          <t>■ 共通</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・使える名前（種別・担当者・カスタム属性など）は backlog-issue-sheet master で確かめられます。</t>
+          <t xml:space="preserve">  ・列は見出しの名前で読みます。要らない列は消して構いません。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・見出しが # で始まる列は読み飛ばします（メモ用）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・カテゴリーなど複数の値は、改行（Alt+Enter）か「,」で区切ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・カスタム属性は、その名前を見出しにした列を足すと使えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・使える名前（種別・担当者・カスタム属性など）は backlog-issue-sheet master で確かめられます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t xml:space="preserve">  ・登録シートでは行の順番が親子関係を表すため、並べ替えないでください。</t>
         </is>
@@ -884,6 +909,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>プロジェクトキー</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>取り込むとき、設定ファイルの project_key と照らし合わせます。違えば何も送りません。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1229,7 +1286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1462,7 +1519,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/templates/課題シート.xlsx
+++ b/templates/課題シート.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -547,57 +547,64 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・backlog-issue-sheet template で作ったひな形と、書き出したファイルには、はじめから入っています。</t>
+          <t xml:space="preserve">  ・メニューの「ひな形を作る」（backlog-issue-sheet template）で作ったひな形と、書き出したファイルには、はじめから入っています。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・空のときは、取り込む先のプロジェクトキーを書いてください。空のままでも取り込めますが、プロジェクトを確かめられず、そのたびに注意が出ます。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>■ 共通</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・列は見出しの名前で読みます。要らない列は消して構いません。</t>
+          <t>■ 共通</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・見出しが # で始まる列は読み飛ばします（メモ用）。</t>
+          <t xml:space="preserve">  ・列は見出しの名前で読みます。要らない列は消して構いません。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・カテゴリーなど複数の値は、改行（Alt+Enter）か「,」で区切ります。</t>
+          <t xml:space="preserve">  ・見出しが # で始まる列は読み飛ばします（メモ用）。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・カスタム属性は、その名前を見出しにした列を足すと使えます。</t>
+          <t xml:space="preserve">  ・カテゴリーなど複数の値は、改行（Alt+Enter）か「,」で区切ります。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ・使える名前（種別・担当者・カスタム属性など）は backlog-issue-sheet master で確かめられます。</t>
+          <t xml:space="preserve">  ・カスタム属性は、その名前を見出しにした列を足すと使えます。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ・使える名前（種別・担当者・カスタム属性など）は、メニューの「使える名前の一覧」（backlog-issue-sheet master）で確かめられます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t xml:space="preserve">  ・登録シートでは行の順番が親子関係を表すため、並べ替えないでください。</t>
         </is>
